--- a/B/chrXI:523927-571556_17_finemapping.xlsx
+++ b/B/chrXI:523927-571556_17_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="3270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3262" uniqueCount="3262">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">4/5</t>
   </si>
   <si>
-    <t xml:space="preserve">317/1989</t>
+    <t xml:space="preserve">325/1989</t>
   </si>
   <si>
     <t xml:space="preserve">YAL012W/YHR208W/YMR083W/YOL086C</t>
@@ -8990,19 +8990,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -9201,21 +9192,6 @@
   </si>
   <si>
     <t xml:space="preserve">MUP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -10260,48 +10236,42 @@
         <v>2988</v>
       </c>
       <c r="Z1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" t="s">
         <v>2989</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>2990</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>2991</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>2992</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>2993</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>2994</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>2995</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>2996</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>2997</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>2998</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>3000</v>
+        <v>2997</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -10355,62 +10325,60 @@
         <v>530545</v>
       </c>
       <c r="U2" t="s">
-        <v>3001</v>
+        <v>2998</v>
       </c>
       <c r="V2" t="n">
         <v>159473</v>
       </c>
       <c r="W2" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-0.0895541760422786</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0186544743983974</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3001</v>
       </c>
       <c r="AD2" t="s">
         <v>19</v>
       </c>
       <c r="AE2" t="s">
-        <v>3004</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3004</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>3005</v>
+        <v>3001</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>3002</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>3006</v>
+        <v>3003</v>
       </c>
       <c r="D3" t="s">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="E3" t="n">
         <v>524433</v>
@@ -10461,53 +10429,51 @@
         <v>526428</v>
       </c>
       <c r="U3" t="s">
-        <v>3008</v>
+        <v>3005</v>
       </c>
       <c r="V3" t="n">
         <v>382030</v>
       </c>
       <c r="W3" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.430479234754563</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0958089673874862</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>3006</v>
       </c>
       <c r="AD3" t="s">
         <v>19</v>
       </c>
       <c r="AE3" t="s">
-        <v>3009</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3009</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>3010</v>
+        <v>3006</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>3007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -10516,7 +10482,7 @@
         <v>1581</v>
       </c>
       <c r="D4" t="s">
-        <v>3011</v>
+        <v>3008</v>
       </c>
       <c r="E4" t="n">
         <v>566095</v>
@@ -10567,59 +10533,57 @@
         <v>570052</v>
       </c>
       <c r="U4" t="s">
-        <v>3012</v>
+        <v>3009</v>
       </c>
       <c r="V4" t="n">
         <v>130799</v>
       </c>
       <c r="W4" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3013</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3010</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.0975497982638852</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0224405715738472</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3011</v>
       </c>
       <c r="AD4" t="s">
         <v>19</v>
       </c>
       <c r="AE4" t="s">
-        <v>3014</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3014</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>3015</v>
+        <v>3011</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>3012</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>3016</v>
+        <v>3013</v>
       </c>
       <c r="D5" t="s">
         <v>69</v>
@@ -10673,62 +10637,60 @@
         <v>566095</v>
       </c>
       <c r="U5" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="V5" t="n">
         <v>30818</v>
       </c>
       <c r="W5" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.458016395867611</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.119496884031621</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3015</v>
       </c>
       <c r="AD5" t="s">
         <v>19</v>
       </c>
       <c r="AE5" t="s">
-        <v>3018</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3018</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>3016</v>
+        <v>3015</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>3013</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>3019</v>
+        <v>3016</v>
       </c>
       <c r="D6" t="s">
-        <v>3020</v>
+        <v>3017</v>
       </c>
       <c r="E6" t="n">
         <v>526428</v>
@@ -10779,59 +10741,57 @@
         <v>559412</v>
       </c>
       <c r="U6" t="s">
-        <v>3001</v>
+        <v>2998</v>
       </c>
       <c r="V6" t="n">
         <v>761486</v>
       </c>
       <c r="W6" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.0809032819987131</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.0226665692601324</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3001</v>
       </c>
       <c r="AD6" t="s">
         <v>19</v>
       </c>
       <c r="AE6" t="s">
-        <v>3004</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3004</v>
-      </c>
-      <c r="AH6" t="n">
+        <v>3001</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2</v>
       </c>
-      <c r="AI6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>3021</v>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>3018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>3022</v>
+        <v>3019</v>
       </c>
       <c r="D7" t="s">
         <v>69</v>
@@ -10885,62 +10845,60 @@
         <v>566095</v>
       </c>
       <c r="U7" t="s">
-        <v>3008</v>
+        <v>3005</v>
       </c>
       <c r="V7" t="n">
         <v>789235</v>
       </c>
       <c r="W7" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.0974529815356133</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.026372017030387</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3006</v>
       </c>
       <c r="AD7" t="s">
         <v>19</v>
       </c>
       <c r="AE7" t="s">
-        <v>3009</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3009</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>3023</v>
+        <v>3006</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>3020</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>3024</v>
+        <v>3021</v>
       </c>
       <c r="D8" t="s">
-        <v>3020</v>
+        <v>3017</v>
       </c>
       <c r="E8" t="n">
         <v>533947</v>
@@ -10991,62 +10949,60 @@
         <v>559412</v>
       </c>
       <c r="U8" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="V8" t="n">
         <v>33598</v>
       </c>
       <c r="W8" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.0809961680944866</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0238647682357341</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3015</v>
       </c>
       <c r="AD8" t="s">
         <v>19</v>
       </c>
       <c r="AE8" t="s">
-        <v>3018</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>3018</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>3024</v>
+        <v>3015</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>3021</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>3025</v>
+        <v>3022</v>
       </c>
       <c r="D9" t="s">
-        <v>3026</v>
+        <v>3023</v>
       </c>
       <c r="E9" t="n">
         <v>516989</v>
@@ -11097,62 +11053,60 @@
         <v>554554</v>
       </c>
       <c r="U9" t="s">
-        <v>3027</v>
+        <v>3024</v>
       </c>
       <c r="V9" t="n">
         <v>826941</v>
       </c>
       <c r="W9" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.10299418274421</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0356779486026452</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3025</v>
       </c>
       <c r="AD9" t="s">
         <v>19</v>
       </c>
       <c r="AE9" t="s">
-        <v>3028</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3028</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>3029</v>
+        <v>3025</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>3026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>3030</v>
+        <v>3027</v>
       </c>
       <c r="D10" t="s">
-        <v>3020</v>
+        <v>3017</v>
       </c>
       <c r="E10" t="n">
         <v>530545</v>
@@ -11203,62 +11157,60 @@
         <v>559412</v>
       </c>
       <c r="U10" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="V10" t="n">
         <v>132244</v>
       </c>
       <c r="W10" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-0.78519311457226</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.270678471851131</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3015</v>
       </c>
       <c r="AD10" t="s">
         <v>19</v>
       </c>
       <c r="AE10" t="s">
-        <v>3018</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>3018</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>3031</v>
+        <v>3015</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>3028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>3032</v>
+        <v>3029</v>
       </c>
       <c r="D11" t="s">
-        <v>3033</v>
+        <v>3030</v>
       </c>
       <c r="E11" t="n">
         <v>524433</v>
@@ -11309,62 +11261,60 @@
         <v>532175</v>
       </c>
       <c r="U11" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="V11" t="n">
         <v>333727</v>
       </c>
       <c r="W11" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.196840553943522</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0751443532268783</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3015</v>
       </c>
       <c r="AD11" t="s">
         <v>19</v>
       </c>
       <c r="AE11" t="s">
-        <v>3018</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3018</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>3034</v>
+        <v>3015</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>3031</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>3035</v>
+        <v>3032</v>
       </c>
       <c r="D12" t="s">
-        <v>3026</v>
+        <v>3023</v>
       </c>
       <c r="E12" t="n">
         <v>530545</v>
@@ -11415,62 +11365,60 @@
         <v>554554</v>
       </c>
       <c r="U12" t="s">
-        <v>3036</v>
+        <v>3033</v>
       </c>
       <c r="V12" t="n">
         <v>175248</v>
       </c>
       <c r="W12" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z12" t="n">
         <v>-0.462890684238825</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.182214553556581</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3034</v>
       </c>
       <c r="AD12" t="s">
         <v>19</v>
       </c>
       <c r="AE12" t="s">
-        <v>3037</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3037</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>3038</v>
+        <v>3034</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>3035</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>3039</v>
+        <v>3036</v>
       </c>
       <c r="D13" t="s">
-        <v>3040</v>
+        <v>3037</v>
       </c>
       <c r="E13" t="n">
         <v>118487</v>
@@ -11521,62 +11469,60 @@
         <v>533947</v>
       </c>
       <c r="U13" t="s">
-        <v>3041</v>
+        <v>3038</v>
       </c>
       <c r="V13" t="n">
         <v>434788</v>
       </c>
       <c r="W13" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.0774049295657438</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0271976245835984</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3039</v>
       </c>
       <c r="AD13" t="s">
         <v>19</v>
       </c>
       <c r="AE13" t="s">
-        <v>3042</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3042</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>3043</v>
+        <v>3039</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>3040</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>3044</v>
+        <v>3041</v>
       </c>
       <c r="D14" t="s">
-        <v>3026</v>
+        <v>3023</v>
       </c>
       <c r="E14" t="n">
         <v>526428</v>
@@ -11627,62 +11573,60 @@
         <v>554554</v>
       </c>
       <c r="U14" t="s">
-        <v>3045</v>
+        <v>3042</v>
       </c>
       <c r="V14" t="n">
         <v>73285</v>
       </c>
       <c r="W14" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.0963029347842895</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0360781467239097</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3043</v>
       </c>
       <c r="AD14" t="s">
         <v>19</v>
       </c>
       <c r="AE14" t="s">
-        <v>3046</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3046</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>3047</v>
+        <v>3043</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>3044</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>3048</v>
+        <v>3045</v>
       </c>
       <c r="D15" t="s">
-        <v>3049</v>
+        <v>3046</v>
       </c>
       <c r="E15" t="n">
         <v>554554</v>
@@ -11733,53 +11677,51 @@
         <v>570508</v>
       </c>
       <c r="U15" t="s">
-        <v>3001</v>
+        <v>2998</v>
       </c>
       <c r="V15" t="n">
         <v>10119</v>
       </c>
       <c r="W15" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3013</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3010</v>
+      </c>
+      <c r="Z15" t="n">
         <v>-0.171422260199945</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0667199591850212</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3001</v>
       </c>
       <c r="AD15" t="s">
         <v>19</v>
       </c>
       <c r="AE15" t="s">
-        <v>3004</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3004</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>3048</v>
+        <v>3001</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>3045</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -11788,7 +11730,7 @@
         <v>1577</v>
       </c>
       <c r="D16" t="s">
-        <v>3020</v>
+        <v>3017</v>
       </c>
       <c r="E16" t="n">
         <v>526428</v>
@@ -11839,62 +11781,60 @@
         <v>559412</v>
       </c>
       <c r="U16" t="s">
-        <v>3050</v>
+        <v>3047</v>
       </c>
       <c r="V16" t="n">
         <v>517532</v>
       </c>
       <c r="W16" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.0741039224899372</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0294198495887748</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3048</v>
       </c>
       <c r="AD16" t="s">
         <v>19</v>
       </c>
       <c r="AE16" t="s">
-        <v>3051</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3051</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>3052</v>
+        <v>3048</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>3049</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>3053</v>
+        <v>3050</v>
       </c>
       <c r="D17" t="s">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="E17" t="n">
         <v>501115</v>
@@ -11945,59 +11885,57 @@
         <v>526428</v>
       </c>
       <c r="U17" t="s">
-        <v>3027</v>
+        <v>3024</v>
       </c>
       <c r="V17" t="n">
         <v>369547</v>
       </c>
       <c r="W17" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.0154590747643097</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.00743597369795533</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3025</v>
       </c>
       <c r="AD17" t="s">
         <v>19</v>
       </c>
       <c r="AE17" t="s">
-        <v>3028</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3028</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>3054</v>
+        <v>3025</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>3051</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>3055</v>
+        <v>3052</v>
       </c>
       <c r="D18" t="s">
         <v>69</v>
@@ -12051,48 +11989,46 @@
         <v>566095</v>
       </c>
       <c r="U18" t="s">
-        <v>3056</v>
+        <v>3053</v>
       </c>
       <c r="V18" t="n">
         <v>599417</v>
       </c>
       <c r="W18" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3003</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3000</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.0702350151430222</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0287809532627484</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3054</v>
       </c>
       <c r="AD18" t="s">
         <v>19</v>
       </c>
       <c r="AE18" t="s">
-        <v>3057</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3057</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>3058</v>
+        <v>3054</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>3055</v>
       </c>
     </row>
   </sheetData>
@@ -12171,37 +12107,28 @@
         <v>2985</v>
       </c>
       <c r="V1" t="s">
-        <v>3059</v>
+        <v>41</v>
       </c>
       <c r="W1" t="s">
-        <v>3060</v>
+        <v>2989</v>
       </c>
       <c r="X1" t="s">
-        <v>3061</v>
+        <v>2990</v>
       </c>
       <c r="Y1" t="s">
-        <v>3062</v>
+        <v>2991</v>
       </c>
       <c r="Z1" t="s">
-        <v>3063</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="AB1" t="s">
-        <v>2994</v>
+        <v>3056</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>2995</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>2998</v>
       </c>
     </row>
     <row r="2">
@@ -12209,10 +12136,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>3065</v>
+        <v>3057</v>
       </c>
       <c r="C2" t="s">
-        <v>3066</v>
+        <v>3058</v>
       </c>
       <c r="D2" t="n">
         <v>499635</v>
@@ -12269,37 +12196,28 @@
         <v>519527</v>
       </c>
       <c r="V2" t="n">
-        <v>-9.06209857704532</v>
+        <v>-0.193121490414779</v>
       </c>
       <c r="W2" t="n">
-        <v>-7.6774890923219</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-3.95690137650604</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2.88283456175028</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-2.62020745906968</v>
+        <v>0.030910721145786</v>
+      </c>
+      <c r="X2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>19</v>
       </c>
       <c r="AA2" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" t="s">
-        <v>19</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>3067</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="3">
@@ -12307,10 +12225,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>3068</v>
+        <v>3060</v>
       </c>
       <c r="C3" t="s">
-        <v>3069</v>
+        <v>3061</v>
       </c>
       <c r="D3" t="n">
         <v>505817</v>
@@ -12367,37 +12285,28 @@
         <v>506898</v>
       </c>
       <c r="V3" t="n">
-        <v>-7.35473108065882</v>
+        <v>-0.283100327111252</v>
       </c>
       <c r="W3" t="n">
-        <v>-3.43732260273754</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.2313468382142</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-2.02363372443473</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-3.61463731957575</v>
+        <v>0.0660954962331395</v>
+      </c>
+      <c r="X3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>19</v>
       </c>
       <c r="AA3" t="s">
         <v>19</v>
       </c>
-      <c r="AB3" t="s">
-        <v>19</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3070</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="4">
@@ -12405,10 +12314,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>3071</v>
+        <v>3063</v>
       </c>
       <c r="C4" t="s">
-        <v>3072</v>
+        <v>3064</v>
       </c>
       <c r="D4" t="n">
         <v>403407</v>
@@ -12465,37 +12374,28 @@
         <v>525256</v>
       </c>
       <c r="V4" t="n">
-        <v>0.959638275872151</v>
+        <v>0.0419000084964671</v>
       </c>
       <c r="W4" t="n">
-        <v>4.62271048841965</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-1.52589131279311</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.3180954692399</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-1.08206943613565</v>
+        <v>0.0354135462638694</v>
+      </c>
+      <c r="X4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>19</v>
       </c>
       <c r="AA4" t="s">
         <v>19</v>
       </c>
-      <c r="AB4" t="s">
-        <v>19</v>
+      <c r="AB4" t="n">
+        <v>0.00082135523613963</v>
       </c>
       <c r="AC4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.00082135523613963</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>3073</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="5">
@@ -12503,10 +12403,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>3074</v>
+        <v>3066</v>
       </c>
       <c r="C5" t="s">
-        <v>3075</v>
+        <v>3067</v>
       </c>
       <c r="D5" t="n">
         <v>860</v>
@@ -12563,37 +12463,28 @@
         <v>520765</v>
       </c>
       <c r="V5" t="n">
-        <v>2.62178964681826</v>
+        <v>0.0693738244723192</v>
       </c>
       <c r="W5" t="n">
-        <v>3.22966665466167</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.0293316184976745</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.701560042055778</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.36211253849194</v>
+        <v>0.0350351709972633</v>
+      </c>
+      <c r="X5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>19</v>
       </c>
       <c r="AA5" t="s">
         <v>19</v>
       </c>
-      <c r="AB5" t="s">
-        <v>19</v>
+      <c r="AB5" t="n">
+        <v>0.00301204819277108</v>
       </c>
       <c r="AC5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.00301204819277108</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>3076</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="6">
@@ -12601,10 +12492,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>3077</v>
+        <v>3069</v>
       </c>
       <c r="C6" t="s">
-        <v>3078</v>
+        <v>3070</v>
       </c>
       <c r="D6" t="n">
         <v>360713</v>
@@ -12661,37 +12552,28 @@
         <v>556518</v>
       </c>
       <c r="V6" t="n">
-        <v>0.225167086204034</v>
+        <v>0.115626315822575</v>
       </c>
       <c r="W6" t="n">
-        <v>2.69321920112197</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.48986317971622</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.51718246897309</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.32504914693564</v>
+        <v>0.0925296777239581</v>
+      </c>
+      <c r="X6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>19</v>
       </c>
       <c r="AA6" t="s">
         <v>19</v>
       </c>
-      <c r="AB6" t="s">
-        <v>19</v>
+      <c r="AB6" t="n">
+        <v>0.00335664335664336</v>
       </c>
       <c r="AC6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.00335664335664336</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>3079</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="7">
@@ -12699,10 +12581,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>3080</v>
+        <v>3072</v>
       </c>
       <c r="C7" t="s">
-        <v>3026</v>
+        <v>3023</v>
       </c>
       <c r="D7" t="n">
         <v>533947</v>
@@ -12759,37 +12641,28 @@
         <v>552770</v>
       </c>
       <c r="V7" t="n">
-        <v>2.17458428745203</v>
+        <v>-0.00934365474241157</v>
       </c>
       <c r="W7" t="n">
-        <v>-3.53282631708648</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.0820943370494678</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.825670531727103</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-1.42939789432461</v>
+        <v>0.0835537536633863</v>
+      </c>
+      <c r="X7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>19</v>
       </c>
       <c r="AA7" t="s">
         <v>19</v>
       </c>
-      <c r="AB7" t="s">
-        <v>19</v>
+      <c r="AB7" t="n">
+        <v>0.00813810110974106</v>
       </c>
       <c r="AC7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.00813810110974106</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>3081</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="8">
@@ -12797,10 +12670,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>3082</v>
+        <v>3074</v>
       </c>
       <c r="C8" t="s">
-        <v>3083</v>
+        <v>3075</v>
       </c>
       <c r="D8" t="n">
         <v>178477</v>
@@ -12857,37 +12730,28 @@
         <v>559666</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.85625665800626</v>
+        <v>-0.0718039055579333</v>
       </c>
       <c r="W8" t="n">
-        <v>1.27846328650807</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.134835866072968</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1.16102738264126</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.03563839779277</v>
+        <v>0.0692921727919061</v>
+      </c>
+      <c r="X8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>19</v>
       </c>
       <c r="AA8" t="s">
         <v>19</v>
       </c>
-      <c r="AB8" t="s">
-        <v>19</v>
+      <c r="AB8" t="n">
+        <v>0.0138958187902431</v>
       </c>
       <c r="AC8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.0138958187902431</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>3084</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="9">
@@ -12895,10 +12759,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>3085</v>
+        <v>3077</v>
       </c>
       <c r="C9" t="s">
-        <v>3086</v>
+        <v>3078</v>
       </c>
       <c r="D9" t="n">
         <v>860</v>
@@ -12955,37 +12819,28 @@
         <v>518198</v>
       </c>
       <c r="V9" t="n">
-        <v>0.812110056540084</v>
+        <v>0.0343929044641309</v>
       </c>
       <c r="W9" t="n">
-        <v>2.23950782849199</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.67830496344322</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.188646163195215</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-2.91689370624435</v>
+        <v>0.265663528166787</v>
+      </c>
+      <c r="X9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>19</v>
       </c>
       <c r="AA9" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" t="s">
-        <v>19</v>
+      <c r="AB9" t="n">
+        <v>0.0146490553831714</v>
       </c>
       <c r="AC9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.0146490553831714</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>3085</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="10">
@@ -12993,10 +12848,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>3087</v>
+        <v>3079</v>
       </c>
       <c r="C10" t="s">
-        <v>3088</v>
+        <v>3080</v>
       </c>
       <c r="D10" t="n">
         <v>194022</v>
@@ -13053,37 +12908,28 @@
         <v>551657</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.519676827038041</v>
+        <v>-0.0179948954895936</v>
       </c>
       <c r="W10" t="n">
-        <v>-3.5684250864776</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.17540063485483</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-1.3066253977081</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-1.5029466188888</v>
+        <v>0.0123773065748654</v>
+      </c>
+      <c r="X10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>19</v>
       </c>
       <c r="AA10" t="s">
         <v>19</v>
       </c>
-      <c r="AB10" t="s">
-        <v>19</v>
+      <c r="AB10" t="n">
+        <v>0.0166406685957501</v>
       </c>
       <c r="AC10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.0166406685957501</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>3089</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="11">
@@ -13091,10 +12937,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>3090</v>
+        <v>3082</v>
       </c>
       <c r="C11" t="s">
-        <v>3091</v>
+        <v>3083</v>
       </c>
       <c r="D11" t="n">
         <v>278682</v>
@@ -13151,37 +12997,28 @@
         <v>522015</v>
       </c>
       <c r="V11" t="n">
-        <v>1.98275202374709</v>
+        <v>0.235251567079322</v>
       </c>
       <c r="W11" t="n">
-        <v>1.91461437968726</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.73060941426707</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.61431710594112</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.9260455737879</v>
+        <v>0.126889551644149</v>
+      </c>
+      <c r="X11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>19</v>
       </c>
       <c r="AA11" t="s">
         <v>19</v>
       </c>
-      <c r="AB11" t="s">
-        <v>19</v>
+      <c r="AB11" t="n">
+        <v>0.0227066974874147</v>
       </c>
       <c r="AC11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.0227066974874147</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>3092</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="12">
@@ -13189,10 +13026,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>3093</v>
+        <v>3085</v>
       </c>
       <c r="C12" t="s">
-        <v>3094</v>
+        <v>3086</v>
       </c>
       <c r="D12" t="n">
         <v>257708</v>
@@ -13249,37 +13086,28 @@
         <v>491364</v>
       </c>
       <c r="V12" t="n">
-        <v>2.64020480560602</v>
+        <v>0.161913394834184</v>
       </c>
       <c r="W12" t="n">
-        <v>0.753775974252867</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.96485251936518</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.97385775753471</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.19909008880418</v>
+        <v>0.124463104973761</v>
+      </c>
+      <c r="X12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>19</v>
       </c>
       <c r="AA12" t="s">
         <v>19</v>
       </c>
-      <c r="AB12" t="s">
-        <v>19</v>
+      <c r="AB12" t="n">
+        <v>0.0241941439455277</v>
       </c>
       <c r="AC12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.0241941439455277</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>3095</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="13">
@@ -13287,10 +13115,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="C13" t="s">
-        <v>3097</v>
+        <v>3089</v>
       </c>
       <c r="D13" t="n">
         <v>860</v>
@@ -13347,37 +13175,28 @@
         <v>548216</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.54827188688186</v>
+        <v>-0.281889975926079</v>
       </c>
       <c r="W13" t="n">
-        <v>0.258244596070857</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-1.54343843779056</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-1.33170629761138</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-3.11412324915639</v>
+        <v>0.194228642886137</v>
+      </c>
+      <c r="X13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>19</v>
       </c>
       <c r="AA13" t="s">
         <v>19</v>
       </c>
-      <c r="AB13" t="s">
-        <v>19</v>
+      <c r="AB13" t="n">
+        <v>0.0253074305547406</v>
       </c>
       <c r="AC13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.0253074305547406</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>3098</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="14">
@@ -13385,10 +13204,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>3099</v>
+        <v>3091</v>
       </c>
       <c r="C14" t="s">
-        <v>3100</v>
+        <v>3092</v>
       </c>
       <c r="D14" t="n">
         <v>194022</v>
@@ -13445,37 +13264,28 @@
         <v>488618</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.79885216820161</v>
+        <v>-0.0647551764237572</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.578756519095719</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-1.00128534064553</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.0831373522112</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-2.63632364622649</v>
+        <v>0.0696093554316154</v>
+      </c>
+      <c r="X14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>19</v>
       </c>
       <c r="AA14" t="s">
         <v>19</v>
       </c>
-      <c r="AB14" t="s">
-        <v>19</v>
+      <c r="AB14" t="n">
+        <v>0.0322412181189171</v>
       </c>
       <c r="AC14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.0322412181189171</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>3101</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="15">
@@ -13483,10 +13293,10 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>3102</v>
+        <v>3094</v>
       </c>
       <c r="C15" t="s">
-        <v>3103</v>
+        <v>3095</v>
       </c>
       <c r="D15" t="n">
         <v>326130</v>
@@ -13543,37 +13353,28 @@
         <v>524103</v>
       </c>
       <c r="V15" t="n">
-        <v>1.80072162717603</v>
+        <v>0.0396121315292863</v>
       </c>
       <c r="W15" t="n">
-        <v>0.284947137167819</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.07932091333579</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-0.113962745686676</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.83858587245491</v>
+        <v>0.0275190321126928</v>
+      </c>
+      <c r="X15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>19</v>
       </c>
       <c r="AA15" t="s">
         <v>19</v>
       </c>
-      <c r="AB15" t="s">
-        <v>19</v>
+      <c r="AB15" t="n">
+        <v>0.0339572827628115</v>
       </c>
       <c r="AC15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.0339572827628115</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>3104</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="16">
@@ -13581,10 +13382,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>3105</v>
+        <v>3097</v>
       </c>
       <c r="C16" t="s">
-        <v>3106</v>
+        <v>3098</v>
       </c>
       <c r="D16" t="n">
         <v>860</v>
@@ -13641,37 +13442,28 @@
         <v>507939</v>
       </c>
       <c r="V16" t="n">
-        <v>2.40898452070332</v>
+        <v>0.0273762229898773</v>
       </c>
       <c r="W16" t="n">
-        <v>0.862020752797711</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.45832241837431</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>-0.97955384095644</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-2.35635407725933</v>
+        <v>0.0479495678363627</v>
+      </c>
+      <c r="X16" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>19</v>
       </c>
       <c r="AA16" t="s">
         <v>19</v>
       </c>
-      <c r="AB16" t="s">
-        <v>19</v>
+      <c r="AB16" t="n">
+        <v>0.0401069518716578</v>
       </c>
       <c r="AC16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.0401069518716578</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>3107</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="17">
@@ -13679,10 +13471,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>3108</v>
+        <v>3100</v>
       </c>
       <c r="C17" t="s">
-        <v>3109</v>
+        <v>3101</v>
       </c>
       <c r="D17" t="n">
         <v>860</v>
@@ -13739,37 +13531,28 @@
         <v>494257</v>
       </c>
       <c r="V17" t="n">
-        <v>0.741126213486962</v>
+        <v>0.0436881056735259</v>
       </c>
       <c r="W17" t="n">
-        <v>1.41542933396333</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.98379201091967</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-2.55653608643768</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.21051862423707</v>
+        <v>0.0675530221425125</v>
+      </c>
+      <c r="X17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>19</v>
       </c>
       <c r="AA17" t="s">
         <v>19</v>
       </c>
-      <c r="AB17" t="s">
-        <v>19</v>
+      <c r="AB17" t="n">
+        <v>0.0416588241337869</v>
       </c>
       <c r="AC17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.0416588241337869</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>3110</v>
+        <v>3102</v>
       </c>
     </row>
   </sheetData>
@@ -13800,34 +13583,34 @@
         <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>3111</v>
+        <v>3103</v>
       </c>
       <c r="G1" t="s">
         <v>1530</v>
       </c>
       <c r="H1" t="s">
-        <v>3112</v>
+        <v>3104</v>
       </c>
       <c r="I1" t="s">
-        <v>3113</v>
+        <v>3105</v>
       </c>
       <c r="J1" t="s">
         <v>1533</v>
       </c>
       <c r="K1" t="s">
-        <v>3114</v>
+        <v>3106</v>
       </c>
       <c r="L1" t="s">
-        <v>3115</v>
+        <v>3107</v>
       </c>
       <c r="M1" t="s">
-        <v>3116</v>
+        <v>3108</v>
       </c>
       <c r="N1" t="s">
-        <v>3117</v>
+        <v>3109</v>
       </c>
       <c r="O1" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="P1" t="s">
         <v>2985</v>
@@ -13847,33 +13630,33 @@
         <v>849</v>
       </c>
       <c r="E2" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F2" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G2" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>3121</v>
+        <v>3113</v>
       </c>
       <c r="K2" t="s">
-        <v>3122</v>
+        <v>3114</v>
       </c>
       <c r="L2" t="s">
-        <v>3121</v>
+        <v>3113</v>
       </c>
       <c r="M2" t="s">
-        <v>3123</v>
+        <v>3115</v>
       </c>
       <c r="N2" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O2" t="s">
-        <v>3125</v>
+        <v>3117</v>
       </c>
       <c r="P2" t="n">
         <v>488194</v>
@@ -13893,33 +13676,33 @@
         <v>918</v>
       </c>
       <c r="E3" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F3" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G3" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>3099</v>
+        <v>3091</v>
       </c>
       <c r="K3" t="s">
-        <v>3127</v>
+        <v>3119</v>
       </c>
       <c r="L3" t="s">
-        <v>3099</v>
+        <v>3091</v>
       </c>
       <c r="M3" t="s">
-        <v>3128</v>
+        <v>3120</v>
       </c>
       <c r="N3" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O3" t="s">
-        <v>3101</v>
+        <v>3093</v>
       </c>
       <c r="P3" t="n">
         <v>489196</v>
@@ -13939,33 +13722,33 @@
         <v>2298</v>
       </c>
       <c r="E4" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F4" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G4" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>3093</v>
+        <v>3085</v>
       </c>
       <c r="K4" t="s">
-        <v>3129</v>
+        <v>3121</v>
       </c>
       <c r="L4" t="s">
-        <v>3093</v>
+        <v>3085</v>
       </c>
       <c r="M4" t="s">
-        <v>3130</v>
+        <v>3122</v>
       </c>
       <c r="N4" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O4" t="s">
-        <v>3095</v>
+        <v>3087</v>
       </c>
       <c r="P4" t="n">
         <v>492512</v>
@@ -13985,33 +13768,33 @@
         <v>3102</v>
       </c>
       <c r="E5" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F5" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G5" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>3108</v>
+        <v>3100</v>
       </c>
       <c r="K5" t="s">
-        <v>3131</v>
+        <v>3123</v>
       </c>
       <c r="L5" t="s">
-        <v>3108</v>
+        <v>3100</v>
       </c>
       <c r="M5" t="s">
-        <v>3132</v>
+        <v>3124</v>
       </c>
       <c r="N5" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O5" t="s">
-        <v>3110</v>
+        <v>3102</v>
       </c>
       <c r="P5" t="n">
         <v>495808</v>
@@ -14031,33 +13814,33 @@
         <v>2256</v>
       </c>
       <c r="E6" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F6" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G6" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>3133</v>
+        <v>3125</v>
       </c>
       <c r="K6" t="s">
-        <v>3134</v>
+        <v>3126</v>
       </c>
       <c r="L6" t="s">
-        <v>3133</v>
+        <v>3125</v>
       </c>
       <c r="M6" t="s">
-        <v>3135</v>
+        <v>3127</v>
       </c>
       <c r="N6" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O6" t="s">
-        <v>3136</v>
+        <v>3128</v>
       </c>
       <c r="P6" t="n">
         <v>498706</v>
@@ -14077,33 +13860,33 @@
         <v>822</v>
       </c>
       <c r="E7" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F7" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G7" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>3137</v>
+        <v>3129</v>
       </c>
       <c r="K7" t="s">
-        <v>3138</v>
+        <v>3130</v>
       </c>
       <c r="L7" t="s">
-        <v>3137</v>
+        <v>3129</v>
       </c>
       <c r="M7" t="s">
-        <v>3139</v>
+        <v>3131</v>
       </c>
       <c r="N7" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O7" t="s">
-        <v>3140</v>
+        <v>3132</v>
       </c>
       <c r="P7" t="n">
         <v>500692</v>
@@ -14123,33 +13906,33 @@
         <v>5052</v>
       </c>
       <c r="E8" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F8" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G8" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>3141</v>
+        <v>3133</v>
       </c>
       <c r="K8" t="s">
-        <v>3142</v>
+        <v>3134</v>
       </c>
       <c r="L8" t="s">
-        <v>3141</v>
+        <v>3133</v>
       </c>
       <c r="M8" t="s">
-        <v>3143</v>
+        <v>3135</v>
       </c>
       <c r="N8" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O8" t="s">
-        <v>3144</v>
+        <v>3136</v>
       </c>
       <c r="P8" t="n">
         <v>503870</v>
@@ -14169,30 +13952,30 @@
         <v>315</v>
       </c>
       <c r="E9" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F9" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G9" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>3145</v>
+        <v>3137</v>
       </c>
       <c r="K9" t="s">
-        <v>3146</v>
+        <v>3138</v>
       </c>
       <c r="L9" t="s">
-        <v>3145</v>
+        <v>3137</v>
       </c>
       <c r="M9" t="s">
-        <v>3147</v>
+        <v>3139</v>
       </c>
       <c r="N9" t="s">
-        <v>3148</v>
+        <v>3140</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
@@ -14213,33 +13996,33 @@
         <v>810</v>
       </c>
       <c r="E10" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F10" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G10" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>3068</v>
+        <v>3060</v>
       </c>
       <c r="K10" t="s">
-        <v>3149</v>
+        <v>3141</v>
       </c>
       <c r="L10" t="s">
-        <v>3068</v>
+        <v>3060</v>
       </c>
       <c r="M10" t="s">
-        <v>3150</v>
+        <v>3142</v>
       </c>
       <c r="N10" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O10" t="s">
-        <v>3070</v>
+        <v>3062</v>
       </c>
       <c r="P10" t="n">
         <v>507302</v>
@@ -14259,33 +14042,33 @@
         <v>615</v>
       </c>
       <c r="E11" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F11" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G11" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>3105</v>
+        <v>3097</v>
       </c>
       <c r="K11" t="s">
-        <v>3151</v>
+        <v>3143</v>
       </c>
       <c r="L11" t="s">
-        <v>3105</v>
+        <v>3097</v>
       </c>
       <c r="M11" t="s">
-        <v>3152</v>
+        <v>3144</v>
       </c>
       <c r="N11" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O11" t="s">
-        <v>3107</v>
+        <v>3099</v>
       </c>
       <c r="P11" t="n">
         <v>508246</v>
@@ -14305,33 +14088,33 @@
         <v>1932</v>
       </c>
       <c r="E12" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F12" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G12" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="K12" t="s">
-        <v>3154</v>
+        <v>3146</v>
       </c>
       <c r="L12" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="M12" t="s">
-        <v>3155</v>
+        <v>3147</v>
       </c>
       <c r="N12" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O12" t="s">
-        <v>3156</v>
+        <v>3148</v>
       </c>
       <c r="P12" t="n">
         <v>509668</v>
@@ -14351,33 +14134,33 @@
         <v>888</v>
       </c>
       <c r="E13" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F13" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G13" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="K13" t="s">
-        <v>3158</v>
+        <v>3150</v>
       </c>
       <c r="L13" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="M13" t="s">
-        <v>3159</v>
+        <v>3151</v>
       </c>
       <c r="N13" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O13" t="s">
-        <v>3160</v>
+        <v>3152</v>
       </c>
       <c r="P13" t="n">
         <v>511354</v>
@@ -14397,33 +14180,33 @@
         <v>1161</v>
       </c>
       <c r="E14" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F14" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G14" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>3161</v>
+        <v>3153</v>
       </c>
       <c r="K14" t="s">
-        <v>3162</v>
+        <v>3154</v>
       </c>
       <c r="L14" t="s">
-        <v>3161</v>
+        <v>3153</v>
       </c>
       <c r="M14" t="s">
-        <v>3163</v>
+        <v>3155</v>
       </c>
       <c r="N14" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O14" t="s">
-        <v>3164</v>
+        <v>3156</v>
       </c>
       <c r="P14" t="n">
         <v>512579</v>
@@ -14443,33 +14226,33 @@
         <v>1809</v>
       </c>
       <c r="E15" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F15" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G15" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>3165</v>
+        <v>3157</v>
       </c>
       <c r="K15" t="s">
-        <v>3166</v>
+        <v>3158</v>
       </c>
       <c r="L15" t="s">
-        <v>3165</v>
+        <v>3157</v>
       </c>
       <c r="M15" t="s">
-        <v>3167</v>
+        <v>3159</v>
       </c>
       <c r="N15" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O15" t="s">
-        <v>3168</v>
+        <v>3160</v>
       </c>
       <c r="P15" t="n">
         <v>515967</v>
@@ -14489,30 +14272,30 @@
         <v>753</v>
       </c>
       <c r="E16" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F16" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G16" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>3085</v>
+        <v>3077</v>
       </c>
       <c r="K16" t="s">
-        <v>3169</v>
+        <v>3161</v>
       </c>
       <c r="L16" t="s">
-        <v>3085</v>
+        <v>3077</v>
       </c>
       <c r="M16" t="s">
-        <v>3170</v>
+        <v>3162</v>
       </c>
       <c r="N16" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O16"/>
       <c r="P16" t="n">
@@ -14533,33 +14316,33 @@
         <v>1098</v>
       </c>
       <c r="E17" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F17" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G17" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>3065</v>
+        <v>3057</v>
       </c>
       <c r="K17" t="s">
-        <v>3171</v>
+        <v>3163</v>
       </c>
       <c r="L17" t="s">
-        <v>3065</v>
+        <v>3057</v>
       </c>
       <c r="M17" t="s">
-        <v>3172</v>
+        <v>3164</v>
       </c>
       <c r="N17" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O17" t="s">
-        <v>3067</v>
+        <v>3059</v>
       </c>
       <c r="P17" t="n">
         <v>520076</v>
@@ -14579,33 +14362,33 @@
         <v>816</v>
       </c>
       <c r="E18" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F18" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G18" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>3074</v>
+        <v>3066</v>
       </c>
       <c r="K18" t="s">
-        <v>3173</v>
+        <v>3165</v>
       </c>
       <c r="L18" t="s">
-        <v>3074</v>
+        <v>3066</v>
       </c>
       <c r="M18" t="s">
-        <v>3174</v>
+        <v>3166</v>
       </c>
       <c r="N18" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O18" t="s">
-        <v>3076</v>
+        <v>3068</v>
       </c>
       <c r="P18" t="n">
         <v>521304</v>
@@ -14625,33 +14408,33 @@
         <v>1332</v>
       </c>
       <c r="E19" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F19" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G19" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>3090</v>
+        <v>3082</v>
       </c>
       <c r="K19" t="s">
-        <v>3175</v>
+        <v>3167</v>
       </c>
       <c r="L19" t="s">
-        <v>3090</v>
+        <v>3082</v>
       </c>
       <c r="M19" t="s">
-        <v>3176</v>
+        <v>3168</v>
       </c>
       <c r="N19" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O19" t="s">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="P19" t="n">
         <v>522680</v>
@@ -14671,30 +14454,30 @@
         <v>552</v>
       </c>
       <c r="E20" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F20" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G20" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>3177</v>
+        <v>3169</v>
       </c>
       <c r="K20" t="s">
-        <v>3178</v>
+        <v>3170</v>
       </c>
       <c r="L20" t="s">
-        <v>3177</v>
+        <v>3169</v>
       </c>
       <c r="M20" t="s">
-        <v>3147</v>
+        <v>3139</v>
       </c>
       <c r="N20" t="s">
-        <v>3148</v>
+        <v>3140</v>
       </c>
       <c r="O20"/>
       <c r="P20" t="n">
@@ -14715,33 +14498,33 @@
         <v>852</v>
       </c>
       <c r="E21" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F21" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G21" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>3102</v>
+        <v>3094</v>
       </c>
       <c r="K21" t="s">
-        <v>3179</v>
+        <v>3171</v>
       </c>
       <c r="L21" t="s">
-        <v>3102</v>
+        <v>3094</v>
       </c>
       <c r="M21" t="s">
-        <v>3180</v>
+        <v>3172</v>
       </c>
       <c r="N21" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O21" t="s">
-        <v>3104</v>
+        <v>3096</v>
       </c>
       <c r="P21" t="n">
         <v>524648</v>
@@ -14761,33 +14544,33 @@
         <v>1254</v>
       </c>
       <c r="E22" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F22" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G22" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>3071</v>
+        <v>3063</v>
       </c>
       <c r="K22" t="s">
-        <v>3181</v>
+        <v>3173</v>
       </c>
       <c r="L22" t="s">
-        <v>3071</v>
+        <v>3063</v>
       </c>
       <c r="M22" t="s">
-        <v>3182</v>
+        <v>3174</v>
       </c>
       <c r="N22" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O22" t="s">
-        <v>3073</v>
+        <v>3065</v>
       </c>
       <c r="P22" t="n">
         <v>526014</v>
@@ -14807,33 +14590,33 @@
         <v>402</v>
       </c>
       <c r="E23" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F23" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G23" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>3183</v>
+        <v>3175</v>
       </c>
       <c r="K23" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="L23" t="s">
-        <v>3183</v>
+        <v>3175</v>
       </c>
       <c r="M23" t="s">
-        <v>3185</v>
+        <v>3177</v>
       </c>
       <c r="N23" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O23" t="s">
-        <v>3186</v>
+        <v>3178</v>
       </c>
       <c r="P23" t="n">
         <v>527030</v>
@@ -14853,33 +14636,33 @@
         <v>2670</v>
       </c>
       <c r="E24" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F24" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G24" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>3187</v>
+        <v>3179</v>
       </c>
       <c r="K24" t="s">
-        <v>3188</v>
+        <v>3180</v>
       </c>
       <c r="L24" t="s">
-        <v>3187</v>
+        <v>3179</v>
       </c>
       <c r="M24" t="s">
-        <v>3189</v>
+        <v>3181</v>
       </c>
       <c r="N24" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O24" t="s">
-        <v>3190</v>
+        <v>3182</v>
       </c>
       <c r="P24" t="n">
         <v>529150</v>
@@ -14899,30 +14682,30 @@
         <v>1257</v>
       </c>
       <c r="E25" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F25" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G25" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>3191</v>
+        <v>3183</v>
       </c>
       <c r="K25" t="s">
-        <v>3192</v>
+        <v>3184</v>
       </c>
       <c r="L25" t="s">
-        <v>3191</v>
+        <v>3183</v>
       </c>
       <c r="M25" t="s">
-        <v>3147</v>
+        <v>3139</v>
       </c>
       <c r="N25" t="s">
-        <v>3148</v>
+        <v>3140</v>
       </c>
       <c r="O25"/>
       <c r="P25" t="n">
@@ -14943,33 +14726,33 @@
         <v>915</v>
       </c>
       <c r="E26" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F26" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G26" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>3193</v>
+        <v>3185</v>
       </c>
       <c r="K26" t="s">
-        <v>3194</v>
+        <v>3186</v>
       </c>
       <c r="L26" t="s">
-        <v>3193</v>
+        <v>3185</v>
       </c>
       <c r="M26" t="s">
-        <v>3195</v>
+        <v>3187</v>
       </c>
       <c r="N26" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O26" t="s">
-        <v>3196</v>
+        <v>3188</v>
       </c>
       <c r="P26" t="n">
         <v>533007</v>
@@ -14989,33 +14772,33 @@
         <v>1215</v>
       </c>
       <c r="E27" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F27" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G27" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>3197</v>
+        <v>3189</v>
       </c>
       <c r="K27" t="s">
-        <v>3198</v>
+        <v>3190</v>
       </c>
       <c r="L27" t="s">
-        <v>3197</v>
+        <v>3189</v>
       </c>
       <c r="M27" t="s">
-        <v>3199</v>
+        <v>3191</v>
       </c>
       <c r="N27" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O27" t="s">
-        <v>3200</v>
+        <v>3192</v>
       </c>
       <c r="P27" t="n">
         <v>534674</v>
@@ -15035,33 +14818,33 @@
         <v>12279</v>
       </c>
       <c r="E28" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F28" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G28" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>3201</v>
+        <v>3193</v>
       </c>
       <c r="K28" t="s">
-        <v>3202</v>
+        <v>3194</v>
       </c>
       <c r="L28" t="s">
-        <v>3201</v>
+        <v>3193</v>
       </c>
       <c r="M28" t="s">
-        <v>3203</v>
+        <v>3195</v>
       </c>
       <c r="N28" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O28" t="s">
-        <v>3204</v>
+        <v>3196</v>
       </c>
       <c r="P28" t="n">
         <v>541786</v>
@@ -15081,33 +14864,33 @@
         <v>876</v>
       </c>
       <c r="E29" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F29" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G29" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="K29" t="s">
-        <v>3205</v>
+        <v>3197</v>
       </c>
       <c r="L29" t="s">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="M29" t="s">
-        <v>3206</v>
+        <v>3198</v>
       </c>
       <c r="N29" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O29" t="s">
-        <v>3098</v>
+        <v>3090</v>
       </c>
       <c r="P29" t="n">
         <v>548654</v>
@@ -15127,33 +14910,33 @@
         <v>1920</v>
       </c>
       <c r="E30" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F30" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G30" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>3207</v>
+        <v>3199</v>
       </c>
       <c r="K30" t="s">
-        <v>3208</v>
+        <v>3200</v>
       </c>
       <c r="L30" t="s">
-        <v>3207</v>
+        <v>3199</v>
       </c>
       <c r="M30" t="s">
-        <v>3209</v>
+        <v>3201</v>
       </c>
       <c r="N30" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O30" t="s">
-        <v>3210</v>
+        <v>3202</v>
       </c>
       <c r="P30" t="n">
         <v>550408</v>
@@ -15173,33 +14956,33 @@
         <v>586</v>
       </c>
       <c r="E31" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F31" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G31" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>3087</v>
+        <v>3079</v>
       </c>
       <c r="K31" t="s">
-        <v>3211</v>
+        <v>3203</v>
       </c>
       <c r="L31" t="s">
-        <v>3087</v>
+        <v>3079</v>
       </c>
       <c r="M31" t="s">
-        <v>3212</v>
+        <v>3204</v>
       </c>
       <c r="N31" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O31" t="s">
-        <v>3089</v>
+        <v>3081</v>
       </c>
       <c r="P31" t="n">
         <v>551950</v>
@@ -15219,33 +15002,33 @@
         <v>1851</v>
       </c>
       <c r="E32" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F32" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G32" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>3080</v>
+        <v>3072</v>
       </c>
       <c r="K32" t="s">
-        <v>3213</v>
+        <v>3205</v>
       </c>
       <c r="L32" t="s">
-        <v>3080</v>
+        <v>3072</v>
       </c>
       <c r="M32" t="s">
-        <v>3214</v>
+        <v>3206</v>
       </c>
       <c r="N32" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O32" t="s">
-        <v>3081</v>
+        <v>3073</v>
       </c>
       <c r="P32" t="n">
         <v>553695</v>
@@ -15265,33 +15048,33 @@
         <v>1188</v>
       </c>
       <c r="E33" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F33" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G33" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>3215</v>
+        <v>3207</v>
       </c>
       <c r="K33" t="s">
-        <v>3216</v>
+        <v>3208</v>
       </c>
       <c r="L33" t="s">
-        <v>3215</v>
+        <v>3207</v>
       </c>
       <c r="M33" t="s">
-        <v>3217</v>
+        <v>3209</v>
       </c>
       <c r="N33" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O33" t="s">
-        <v>3218</v>
+        <v>3210</v>
       </c>
       <c r="P33" t="n">
         <v>555580</v>
@@ -15311,33 +15094,33 @@
         <v>825</v>
       </c>
       <c r="E34" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F34" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G34" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>3077</v>
+        <v>3069</v>
       </c>
       <c r="K34" t="s">
-        <v>3219</v>
+        <v>3211</v>
       </c>
       <c r="L34" t="s">
-        <v>3077</v>
+        <v>3069</v>
       </c>
       <c r="M34" t="s">
-        <v>3220</v>
+        <v>3212</v>
       </c>
       <c r="N34" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O34" t="s">
-        <v>3079</v>
+        <v>3071</v>
       </c>
       <c r="P34" t="n">
         <v>556930</v>
@@ -15357,33 +15140,33 @@
         <v>1278</v>
       </c>
       <c r="E35" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F35" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G35" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>3221</v>
+        <v>3213</v>
       </c>
       <c r="K35" t="s">
-        <v>3222</v>
+        <v>3214</v>
       </c>
       <c r="L35" t="s">
-        <v>3221</v>
+        <v>3213</v>
       </c>
       <c r="M35" t="s">
-        <v>3223</v>
+        <v>3215</v>
       </c>
       <c r="N35" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O35" t="s">
-        <v>3224</v>
+        <v>3216</v>
       </c>
       <c r="P35" t="n">
         <v>558316</v>
@@ -15403,33 +15186,33 @@
         <v>987</v>
       </c>
       <c r="E36" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F36" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G36" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>3082</v>
+        <v>3074</v>
       </c>
       <c r="K36" t="s">
-        <v>3225</v>
+        <v>3217</v>
       </c>
       <c r="L36" t="s">
-        <v>3082</v>
+        <v>3074</v>
       </c>
       <c r="M36" t="s">
-        <v>3226</v>
+        <v>3218</v>
       </c>
       <c r="N36" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O36" t="s">
-        <v>3084</v>
+        <v>3076</v>
       </c>
       <c r="P36" t="n">
         <v>560159</v>
@@ -15449,33 +15232,33 @@
         <v>1509</v>
       </c>
       <c r="E37" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F37" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G37" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>3227</v>
+        <v>3219</v>
       </c>
       <c r="K37" t="s">
-        <v>3228</v>
+        <v>3220</v>
       </c>
       <c r="L37" t="s">
-        <v>3227</v>
+        <v>3219</v>
       </c>
       <c r="M37" t="s">
-        <v>3229</v>
+        <v>3221</v>
       </c>
       <c r="N37" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O37" t="s">
-        <v>3230</v>
+        <v>3222</v>
       </c>
       <c r="P37" t="n">
         <v>561543</v>
@@ -15495,33 +15278,33 @@
         <v>2592</v>
       </c>
       <c r="E38" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F38" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G38" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="K38" t="s">
-        <v>3232</v>
+        <v>3224</v>
       </c>
       <c r="L38" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="M38" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
       <c r="N38" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O38" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="P38" t="n">
         <v>563842</v>
@@ -15541,33 +15324,33 @@
         <v>594</v>
       </c>
       <c r="E39" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F39" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G39" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
       <c r="K39" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="L39" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
       <c r="M39" t="s">
-        <v>3237</v>
+        <v>3229</v>
       </c>
       <c r="N39" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O39" t="s">
-        <v>3238</v>
+        <v>3230</v>
       </c>
       <c r="P39" t="n">
         <v>565596</v>
@@ -15587,33 +15370,33 @@
         <v>1086</v>
       </c>
       <c r="E40" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F40" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G40" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
       <c r="K40" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
       <c r="L40" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
       <c r="M40" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="N40" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O40" t="s">
-        <v>3242</v>
+        <v>3234</v>
       </c>
       <c r="P40" t="n">
         <v>566656</v>
@@ -15633,33 +15416,33 @@
         <v>2232</v>
       </c>
       <c r="E41" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F41" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G41" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
       <c r="K41" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="L41" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
       <c r="M41" t="s">
-        <v>3245</v>
+        <v>3237</v>
       </c>
       <c r="N41" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O41" t="s">
-        <v>3246</v>
+        <v>3238</v>
       </c>
       <c r="P41" t="n">
         <v>569034</v>
@@ -15679,33 +15462,33 @@
         <v>582</v>
       </c>
       <c r="E42" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F42" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G42" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H42"/>
       <c r="I42"/>
       <c r="J42" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="K42" t="s">
-        <v>3248</v>
+        <v>3240</v>
       </c>
       <c r="L42" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="M42" t="s">
-        <v>3249</v>
+        <v>3241</v>
       </c>
       <c r="N42" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O42" t="s">
-        <v>3250</v>
+        <v>3242</v>
       </c>
       <c r="P42" t="n">
         <v>570618</v>
@@ -15725,33 +15508,33 @@
         <v>1782</v>
       </c>
       <c r="E43" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F43" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G43" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43" t="s">
-        <v>3251</v>
+        <v>3243</v>
       </c>
       <c r="K43" t="s">
-        <v>3252</v>
+        <v>3244</v>
       </c>
       <c r="L43" t="s">
-        <v>3251</v>
+        <v>3243</v>
       </c>
       <c r="M43" t="s">
-        <v>3253</v>
+        <v>3245</v>
       </c>
       <c r="N43" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O43" t="s">
-        <v>3254</v>
+        <v>3246</v>
       </c>
       <c r="P43" t="n">
         <v>572502</v>
@@ -15771,30 +15554,30 @@
         <v>1059</v>
       </c>
       <c r="E44" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F44" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G44" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44" t="s">
-        <v>3255</v>
+        <v>3247</v>
       </c>
       <c r="K44" t="s">
-        <v>3256</v>
+        <v>3248</v>
       </c>
       <c r="L44" t="s">
-        <v>3255</v>
+        <v>3247</v>
       </c>
       <c r="M44" t="s">
-        <v>3147</v>
+        <v>3139</v>
       </c>
       <c r="N44" t="s">
-        <v>3148</v>
+        <v>3140</v>
       </c>
       <c r="O44"/>
       <c r="P44" t="n">
@@ -15815,33 +15598,33 @@
         <v>1047</v>
       </c>
       <c r="E45" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F45" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G45" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="K45" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="L45" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="M45" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="N45" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O45" t="s">
-        <v>3260</v>
+        <v>3252</v>
       </c>
       <c r="P45" t="n">
         <v>575457</v>
@@ -15861,33 +15644,33 @@
         <v>1689</v>
       </c>
       <c r="E46" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F46" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G46" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46" t="s">
-        <v>3261</v>
+        <v>3253</v>
       </c>
       <c r="K46" t="s">
-        <v>3262</v>
+        <v>3254</v>
       </c>
       <c r="L46" t="s">
-        <v>3261</v>
+        <v>3253</v>
       </c>
       <c r="M46" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="N46" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O46" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="P46" t="n">
         <v>577279</v>
@@ -15907,30 +15690,30 @@
         <v>321</v>
       </c>
       <c r="E47" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F47" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G47" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47" t="s">
-        <v>3265</v>
+        <v>3257</v>
       </c>
       <c r="K47" t="s">
-        <v>3266</v>
+        <v>3258</v>
       </c>
       <c r="L47" t="s">
-        <v>3265</v>
+        <v>3257</v>
       </c>
       <c r="M47" t="s">
-        <v>3147</v>
+        <v>3139</v>
       </c>
       <c r="N47" t="s">
-        <v>3148</v>
+        <v>3140</v>
       </c>
       <c r="O47"/>
       <c r="P47" t="n">
@@ -15951,33 +15734,33 @@
         <v>468</v>
       </c>
       <c r="E48" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="F48" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="G48" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="H48"/>
       <c r="I48"/>
       <c r="J48" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="K48" t="s">
-        <v>3268</v>
+        <v>3260</v>
       </c>
       <c r="L48" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="M48" t="s">
-        <v>3170</v>
+        <v>3162</v>
       </c>
       <c r="N48" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="O48" t="s">
-        <v>3269</v>
+        <v>3261</v>
       </c>
       <c r="P48" t="n">
         <v>579442</v>
@@ -48573,7 +48356,7 @@
         <v>1557</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00277438742620318</v>
+        <v>0.00305535715874791</v>
       </c>
       <c r="H4" t="n">
         <v>0.0130603331895504</v>
